--- a/SEM 8/Progress.xlsx
+++ b/SEM 8/Progress.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Degree\SEM 7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\degree\SEM 8\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482F387F-F92A-4B3A-8283-7A0358D0EB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F85941-2AE7-4774-B36C-6F399CBADA7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="34">
   <si>
     <t>EXP1</t>
   </si>
@@ -494,14 +494,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:H32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="1"/>
-    <col min="2" max="8" width="15.77734375" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="8.85546875" style="1"/>
+    <col min="2" max="8" width="15.7109375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="22.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>28</v>
       </c>
@@ -521,7 +521,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
@@ -544,7 +544,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
@@ -567,7 +567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>2</v>
       </c>
@@ -590,7 +590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>3</v>
       </c>
@@ -613,7 +613,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>4</v>
       </c>
@@ -636,7 +636,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
@@ -659,7 +659,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>6</v>
       </c>
@@ -682,7 +682,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
@@ -705,7 +705,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
@@ -728,7 +728,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
@@ -751,7 +751,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
@@ -774,7 +774,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
@@ -797,7 +797,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
@@ -820,7 +820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>25</v>
       </c>
@@ -843,7 +843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>26</v>
       </c>
@@ -866,28 +866,16 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="3"/>
-      <c r="C19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>13</v>
       </c>
@@ -910,7 +898,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>14</v>
       </c>
@@ -933,7 +921,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>16</v>
       </c>
@@ -956,7 +944,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>17</v>
       </c>
@@ -979,7 +967,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>18</v>
       </c>
@@ -1002,7 +990,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>27</v>
       </c>
@@ -1025,10 +1013,10 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
     </row>
-    <row r="27" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>19</v>
       </c>
@@ -1051,7 +1039,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
         <v>20</v>
       </c>
@@ -1074,7 +1062,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>21</v>
       </c>
@@ -1097,7 +1085,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
         <v>22</v>
       </c>
@@ -1120,7 +1108,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
         <v>23</v>
       </c>
@@ -1143,7 +1131,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
         <v>24</v>
       </c>
